--- a/ksoft/docs/records/Sales_Channel_Records.xlsx
+++ b/ksoft/docs/records/Sales_Channel_Records.xlsx
@@ -2654,13 +2654,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4981E9BD-CF39-4E72-9FAE-614128048BFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1B0E90F-2598-463F-AA67-89A100515886}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3750EC2C-AA75-4E09-A61B-5AC9F03D1CE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA96F621-C1F4-46C2-8995-DBB4AF8386B2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C08A49F9-9E3F-4CD9-9361-9EBBF3470618}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B71DC425-216C-4106-A1D0-6FE421DEF976}"/>
 </file>
--- a/ksoft/docs/records/Sales_Channel_Records.xlsx
+++ b/ksoft/docs/records/Sales_Channel_Records.xlsx
@@ -2654,13 +2654,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1B0E90F-2598-463F-AA67-89A100515886}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4981E9BD-CF39-4E72-9FAE-614128048BFC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA96F621-C1F4-46C2-8995-DBB4AF8386B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3750EC2C-AA75-4E09-A61B-5AC9F03D1CE2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B71DC425-216C-4106-A1D0-6FE421DEF976}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C08A49F9-9E3F-4CD9-9361-9EBBF3470618}"/>
 </file>